--- a/reports/Summary_Report.xlsx
+++ b/reports/Summary_Report.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>460</v>
+        <v>300</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>450</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>97.83</v>
+        <v>97.67</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Summary_Report.xlsx
+++ b/reports/Summary_Report.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>97.67</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Summary_Report.xlsx
+++ b/reports/Summary_Report.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>100</v>
+        <v>99.33</v>
       </c>
     </row>
   </sheetData>
